--- a/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов Prophet.xlsx
+++ b/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов Prophet.xlsx
@@ -478,31 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>84.48999999999999</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>69.47</v>
+        <v>57.62</v>
       </c>
       <c r="F2" t="n">
-        <v>10.15</v>
+        <v>8.69</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[560.8, 575.4, 600.34]</t>
+          <t>[479.03, 793.29, 667.76]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[544.33, 634.45, 733.22]</t>
+          <t>[495.67, 679.44, 710.13]</t>
         </is>
       </c>
     </row>
@@ -514,31 +514,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>96.61</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>90.90000000000001</v>
+        <v>78.27</v>
       </c>
       <c r="F3" t="n">
-        <v>13.06</v>
+        <v>10.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[573.17, 596.71, 611.22]</t>
+          <t>[796.53, 669.11, 766.39]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[634.45, 733.22, 686.11]</t>
+          <t>[679.44, 710.13, 843.07]</t>
         </is>
       </c>
     </row>
@@ -550,31 +550,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84.19</v>
+        <v>57.51</v>
       </c>
       <c r="E4" t="n">
-        <v>71.73</v>
+        <v>53.16</v>
       </c>
       <c r="F4" t="n">
-        <v>9.960000000000001</v>
+        <v>6.86</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[605.2, 619.35, 777.0]</t>
+          <t>[664.6, 760.03, 686.29]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[733.22, 686.11, 756.58]</t>
+          <t>[710.13, 843.07, 717.2]</t>
         </is>
       </c>
     </row>
@@ -586,31 +586,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45.54</v>
+        <v>51.93</v>
       </c>
       <c r="E5" t="n">
-        <v>44.58</v>
+        <v>45.9</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[628.64, 792.25, 784.77]</t>
+          <t>[762.84, 688.91, 577.37]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[686.11, 756.58, 825.36]</t>
+          <t>[843.07, 717.2, 606.56]</t>
         </is>
       </c>
     </row>
@@ -622,31 +622,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.38</v>
+        <v>127.52</v>
       </c>
       <c r="E6" t="n">
-        <v>30.73</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>4.32</v>
+        <v>11.49</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[797.97, 791.52, 482.77]</t>
+          <t>[693.07, 581.59, 589.64]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[756.58, 825.36, 499.73]</t>
+          <t>[717.2, 606.56, 807.76]</t>
         </is>
       </c>
     </row>
@@ -658,31 +658,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26.55</v>
+        <v>155.53</v>
       </c>
       <c r="E7" t="n">
-        <v>25.14</v>
+        <v>132.75</v>
       </c>
       <c r="F7" t="n">
-        <v>4.06</v>
+        <v>16.81</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[788.22, 479.64, 477.47]</t>
+          <t>[583.97, 592.52, 639.27]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[825.36, 499.73, 495.67]</t>
+          <t>[606.56, 807.76, 799.68]</t>
         </is>
       </c>
     </row>
@@ -694,31 +694,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67.42</v>
+        <v>173.3</v>
       </c>
       <c r="E8" t="n">
-        <v>49.46</v>
+        <v>170.64</v>
       </c>
       <c r="F8" t="n">
-        <v>7.89</v>
+        <v>21.26</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[481.91, 479.35, 793.7]</t>
+          <t>[595.17, 642.71, 656.04]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[499.73, 495.67, 679.44]</t>
+          <t>[807.76, 799.68, 798.4]</t>
         </is>
       </c>
     </row>
@@ -730,31 +730,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70.79000000000001</v>
+        <v>102.16</v>
       </c>
       <c r="E9" t="n">
-        <v>57.62</v>
+        <v>88.23</v>
       </c>
       <c r="F9" t="n">
-        <v>8.69</v>
+        <v>11.02</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[479.03, 793.29, 667.76]</t>
+          <t>[666.51, 683.0, 836.05]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[495.67, 679.44, 710.13]</t>
+          <t>[799.68, 798.4, 819.95]</t>
         </is>
       </c>
     </row>
@@ -766,31 +766,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.20999999999999</v>
+        <v>63.59</v>
       </c>
       <c r="E10" t="n">
-        <v>78.27</v>
+        <v>58.57</v>
       </c>
       <c r="F10" t="n">
-        <v>10.7</v>
+        <v>7.09</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[796.53, 669.11, 766.39]</t>
+          <t>[705.05, 864.68, 872.16]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[679.44, 710.13, 843.07]</t>
+          <t>[798.4, 819.95, 909.79]</t>
         </is>
       </c>
     </row>
@@ -802,31 +802,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>57.51</v>
+        <v>37.53</v>
       </c>
       <c r="E11" t="n">
-        <v>53.16</v>
+        <v>34.78</v>
       </c>
       <c r="F11" t="n">
-        <v>6.86</v>
+        <v>4.65</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[664.6, 760.03, 686.29]</t>
+          <t>[874.52, 882.6, 548.11]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[710.13, 843.07, 717.2]</t>
+          <t>[819.95, 909.79, 525.54]</t>
         </is>
       </c>
     </row>
@@ -838,31 +838,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>175.68</v>
+        <v>151.75</v>
       </c>
       <c r="E12" t="n">
-        <v>114.78</v>
+        <v>147.48</v>
       </c>
       <c r="F12" t="n">
-        <v>5.24</v>
+        <v>8.65</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[1175.37, 520.72, 2427.18]</t>
+          <t>[1366.39, 1863.17, 1538.39]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[1205.91, 531.99, 2729.71]</t>
+          <t>[1502.85, 1973.46, 1734.09]</t>
         </is>
       </c>
     </row>
@@ -874,31 +874,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>248.47</v>
+        <v>148.33</v>
       </c>
       <c r="E13" t="n">
-        <v>206.42</v>
+        <v>143.98</v>
       </c>
       <c r="F13" t="n">
-        <v>10.07</v>
+        <v>7.15</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[521.11, 2429.09, 1487.46]</t>
+          <t>[1875.76, 1549.73, 2409.6]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[531.99, 2729.71, 1795.23]</t>
+          <t>[1973.46, 1734.09, 2559.49]</t>
         </is>
       </c>
     </row>
@@ -910,31 +910,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>323</v>
+        <v>190.13</v>
       </c>
       <c r="E14" t="n">
-        <v>322.21</v>
+        <v>186.19</v>
       </c>
       <c r="F14" t="n">
-        <v>19.04</v>
+        <v>7.45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[2427.97, 1484.08, 876.95]</t>
+          <t>[1553.95, 2417.14, 3927.67]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[2729.71, 1795.23, 1230.68]</t>
+          <t>[1734.09, 2559.49, 3691.59]</t>
         </is>
       </c>
     </row>
@@ -946,31 +946,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>306.58</v>
+        <v>181.1</v>
       </c>
       <c r="E15" t="n">
-        <v>304.85</v>
+        <v>159.16</v>
       </c>
       <c r="F15" t="n">
-        <v>19.62</v>
+        <v>6.15</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[1493.61, 884.5, 1648.34]</t>
+          <t>[2440.05, 3970.68, 1188.33]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[1795.23, 1230.68, 1915.07]</t>
+          <t>[2559.49, 3691.59, 1267.28]</t>
         </is>
       </c>
     </row>
@@ -982,31 +982,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>257.21</v>
+        <v>193.36</v>
       </c>
       <c r="E16" t="n">
-        <v>250.3</v>
+        <v>142.92</v>
       </c>
       <c r="F16" t="n">
-        <v>18.22</v>
+        <v>7.04</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[900.56, 1682.71, 1011.29]</t>
+          <t>[4018.19, 1204.42, 497.5]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[1230.68, 1915.07, 1199.71]</t>
+          <t>[3691.59, 1267.28, 536.79]</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1018,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>164.92</v>
+        <v>256.37</v>
       </c>
       <c r="E17" t="n">
-        <v>164.58</v>
+        <v>179.5</v>
       </c>
       <c r="F17" t="n">
-        <v>10.96</v>
+        <v>9.02</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[1740.79, 1049.98, 1333.13]</t>
+          <t>[1205.76, 497.86, 2491.58]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[1915.07, 1199.71, 1502.85]</t>
+          <t>[1267.28, 536.79, 2929.62]</t>
         </is>
       </c>
     </row>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>139.12</v>
+        <v>284</v>
       </c>
       <c r="E18" t="n">
-        <v>138.86</v>
+        <v>235.69</v>
       </c>
       <c r="F18" t="n">
-        <v>9.31</v>
+        <v>11.68</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[1064.23, 1352.29, 1842.91]</t>
+          <t>[499.98, 2505.06, 1549.35]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[1199.71, 1502.85, 1973.46]</t>
+          <t>[536.79, 2929.62, 1795.06]</t>
         </is>
       </c>
     </row>
@@ -1090,31 +1090,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>151.75</v>
+        <v>279.38</v>
       </c>
       <c r="E19" t="n">
-        <v>147.48</v>
+        <v>271.6</v>
       </c>
       <c r="F19" t="n">
-        <v>8.65</v>
+        <v>14.67</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[1366.39, 1863.17, 1538.39]</t>
+          <t>[2569.93, 1592.23, 983.21]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[1502.85, 1973.46, 1734.09]</t>
+          <t>[2929.62, 1795.06, 1235.48]</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1126,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>148.33</v>
+        <v>204.83</v>
       </c>
       <c r="E20" t="n">
-        <v>143.98</v>
+        <v>202.94</v>
       </c>
       <c r="F20" t="n">
-        <v>7.15</v>
+        <v>12.71</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[1875.76, 1549.73, 2409.6]</t>
+          <t>[1631.09, 1008.65, 1834.12]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[1973.46, 1734.09, 2559.49]</t>
+          <t>[1795.06, 1235.48, 2052.14]</t>
         </is>
       </c>
     </row>
@@ -1162,31 +1162,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>190.13</v>
+        <v>164.55</v>
       </c>
       <c r="E21" t="n">
-        <v>186.19</v>
+        <v>156.28</v>
       </c>
       <c r="F21" t="n">
-        <v>7.45</v>
+        <v>10.73</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[1553.95, 2417.14, 3927.67]</t>
+          <t>[1029.53, 1874.56, 1158.74]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[1734.09, 2559.49, 3691.59]</t>
+          <t>[1235.48, 2052.14, 1244.06]</t>
         </is>
       </c>
     </row>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>731.39</v>
+        <v>1407.41</v>
       </c>
       <c r="E22" t="n">
-        <v>510.2</v>
+        <v>1088.52</v>
       </c>
       <c r="F22" t="n">
-        <v>20.72</v>
+        <v>31.45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[768.33, 474.55, 2431.52]</t>
+          <t>[1568.47, 2128.46, 1397.5]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[1063.19, 470.8, 3663.52]</t>
+          <t>[2521.78, 4370.94, 1327.73]</t>
         </is>
       </c>
     </row>
@@ -1234,31 +1234,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>624.4</v>
+        <v>1329.47</v>
       </c>
       <c r="E23" t="n">
-        <v>382.74</v>
+        <v>1023.77</v>
       </c>
       <c r="F23" t="n">
-        <v>13.34</v>
+        <v>28.65</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[492.19, 2583.25, 732.59]</t>
+          <t>[2207.92, 1456.81, 2133.71]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[470.8, 3663.52, 779.14]</t>
+          <t>[4370.94, 1327.73, 2912.92]</t>
         </is>
       </c>
     </row>
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>658.12</v>
+        <v>1650.83</v>
       </c>
       <c r="E24" t="n">
-        <v>487.66</v>
+        <v>1208.73</v>
       </c>
       <c r="F24" t="n">
-        <v>22.53</v>
+        <v>24.23</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[2571.42, 731.41, 698.02]</t>
+          <t>[1569.54, 2313.93, 5428.5]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[3663.52, 779.14, 1021.16]</t>
+          <t>[1327.73, 2912.92, 8213.9]</t>
         </is>
       </c>
     </row>
@@ -1306,31 +1306,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>372.23</v>
+        <v>1640.81</v>
       </c>
       <c r="E25" t="n">
-        <v>301.39</v>
+        <v>1239.12</v>
       </c>
       <c r="F25" t="n">
-        <v>17.33</v>
+        <v>29.25</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[746.87, 716.61, 2580.46]</t>
+          <t>[2333.62, 5457.96, 731.45]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[779.14, 1021.16, 3147.81]</t>
+          <t>[2912.92, 8213.9, 1113.56]</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>387.39</v>
+        <v>1375.24</v>
       </c>
       <c r="E26" t="n">
-        <v>351.75</v>
+        <v>906.47</v>
       </c>
       <c r="F26" t="n">
-        <v>22.38</v>
+        <v>21.4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[718.08, 2577.44, 757.94]</t>
+          <t>[5855.01, 784.09, 557.95]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[1021.16, 3147.81, 939.73]</t>
+          <t>[8213.9, 1113.56, 526.89]</t>
         </is>
       </c>
     </row>
@@ -1378,31 +1378,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>664.71</v>
+        <v>438.61</v>
       </c>
       <c r="E27" t="n">
-        <v>562.0700000000001</v>
+        <v>349</v>
       </c>
       <c r="F27" t="n">
-        <v>24.53</v>
+        <v>18.65</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[2644.79, 779.7, 1498.61]</t>
+          <t>[829.47, 587.85, 3020.46]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[3147.81, 939.73, 2521.78]</t>
+          <t>[1113.56, 526.89, 3722.4]</t>
         </is>
       </c>
     </row>
@@ -1414,31 +1414,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1438.07</v>
+        <v>344.51</v>
       </c>
       <c r="E28" t="n">
-        <v>1135.96</v>
+        <v>247</v>
       </c>
       <c r="F28" t="n">
-        <v>35.39</v>
+        <v>13.47</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[799.67, 1537.98, 2086.94]</t>
+          <t>[604.95, 3135.75, 851.63]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[939.73, 2521.78, 4370.94]</t>
+          <t>[526.89, 3722.4, 775.33]</t>
         </is>
       </c>
     </row>
@@ -1450,31 +1450,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1407.41</v>
+        <v>320.43</v>
       </c>
       <c r="E29" t="n">
-        <v>1088.52</v>
+        <v>222.34</v>
       </c>
       <c r="F29" t="n">
-        <v>31.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[1568.47, 2128.46, 1397.5]</t>
+          <t>[3175.16, 861.42, 903.38]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[2521.78, 4370.94, 1327.73]</t>
+          <t>[3722.4, 775.33, 937.06]</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1486,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1329.47</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1023.77</v>
+        <v>54.7</v>
       </c>
       <c r="F30" t="n">
-        <v>28.65</v>
+        <v>5.48</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[2207.92, 1456.81, 2133.71]</t>
+          <t>[885.7, 929.91, 3196.74]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[4370.94, 1327.73, 2912.92]</t>
+          <t>[775.33, 937.06, 3243.32]</t>
         </is>
       </c>
     </row>
@@ -1522,31 +1522,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1650.83</v>
+        <v>19.83</v>
       </c>
       <c r="E31" t="n">
-        <v>1208.73</v>
+        <v>14.71</v>
       </c>
       <c r="F31" t="n">
-        <v>24.23</v>
+        <v>1.38</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[1569.54, 2313.93, 5428.5]</t>
+          <t>[940.95, 3236.5, 984.36]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[1327.73, 2912.92, 8213.9]</t>
+          <t>[937.06, 3243.32, 950.93]</t>
         </is>
       </c>
     </row>
@@ -1558,31 +1558,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>26.83</v>
+        <v>51.29</v>
       </c>
       <c r="E32" t="n">
-        <v>22.96</v>
+        <v>48.09</v>
       </c>
       <c r="F32" t="n">
-        <v>3.7</v>
+        <v>5.05</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[518.56, 589.51, 1041.79]</t>
+          <t>[954.71, 1052.88, 863.72]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[481.67, 585.47, 1013.82]</t>
+          <t>[921.73, 1014.74, 936.86]</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1594,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.96</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>12.73</v>
+        <v>70.45</v>
       </c>
       <c r="F33" t="n">
-        <v>1.51</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[585.14, 1027.87, 747.15]</t>
+          <t>[1049.65, 860.65, 813.91]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[585.47, 1013.82, 770.96]</t>
+          <t>[1014.74, 936.86, 713.69]</t>
         </is>
       </c>
     </row>
@@ -1630,31 +1630,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>27.84</v>
+        <v>158.23</v>
       </c>
       <c r="E34" t="n">
-        <v>25.15</v>
+        <v>139.87</v>
       </c>
       <c r="F34" t="n">
-        <v>3.29</v>
+        <v>11.65</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[1023.76, 744.63, 676.49]</t>
+          <t>[858.92, 811.48, 1642.49]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[1013.82, 770.96, 715.65]</t>
+          <t>[936.86, 713.69, 1886.37]</t>
         </is>
       </c>
     </row>
@@ -1666,31 +1666,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>93.84999999999999</v>
+        <v>144.27</v>
       </c>
       <c r="E35" t="n">
-        <v>74.22</v>
+        <v>111.64</v>
       </c>
       <c r="F35" t="n">
-        <v>4.99</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[743.48, 675.61, 2516.21]</t>
+          <t>[819.22, 1659.88, 491.44]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[770.96, 715.65, 2671.34]</t>
+          <t>[713.69, 1886.37, 488.55]</t>
         </is>
       </c>
     </row>
@@ -1702,31 +1702,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>85.73999999999999</v>
+        <v>143.73</v>
       </c>
       <c r="E36" t="n">
-        <v>63.74</v>
+        <v>91.02</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>5.88</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[678.4, 2527.97, 745.03]</t>
+          <t>[1638.31, 483.96, 554.18]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[715.65, 2671.34, 734.44]</t>
+          <t>[1886.37, 488.55, 574.6]</t>
         </is>
       </c>
     </row>
@@ -1738,31 +1738,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>81.42</v>
+        <v>14.76</v>
       </c>
       <c r="E37" t="n">
-        <v>60.29</v>
+        <v>12.14</v>
       </c>
       <c r="F37" t="n">
-        <v>3.41</v>
+        <v>1.59</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[2534.38, 747.26, 952.8]</t>
+          <t>[490.56, 562.74, 964.26]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[2671.34, 734.44, 921.73]</t>
+          <t>[488.55, 574.6, 986.83]</t>
         </is>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>33.72</v>
+        <v>53.75</v>
       </c>
       <c r="E38" t="n">
-        <v>32</v>
+        <v>41.61</v>
       </c>
       <c r="F38" t="n">
-        <v>3.49</v>
+        <v>5.15</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[751.66, 958.68, 1056.56]</t>
+          <t>[562.61, 963.27, 723.58]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[734.44, 921.73, 1014.74]</t>
+          <t>[574.6, 986.83, 812.85]</t>
         </is>
       </c>
     </row>
@@ -1810,31 +1810,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>51.29</v>
+        <v>75.64</v>
       </c>
       <c r="E39" t="n">
-        <v>48.09</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>5.05</v>
+        <v>8.51</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[954.71, 1052.88, 863.72]</t>
+          <t>[965.35, 725.25, 660.9]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[921.73, 1014.74, 936.86]</t>
+          <t>[986.83, 812.85, 755.93]</t>
         </is>
       </c>
     </row>
@@ -1846,31 +1846,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>75.43000000000001</v>
+        <v>316.68</v>
       </c>
       <c r="E40" t="n">
-        <v>70.45</v>
+        <v>237.64</v>
       </c>
       <c r="F40" t="n">
-        <v>8.539999999999999</v>
+        <v>13.65</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[1049.65, 860.65, 813.91]</t>
+          <t>[726.92, 662.57, 2428.13]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[1014.74, 936.86, 713.69]</t>
+          <t>[812.85, 755.93, 2961.75]</t>
         </is>
       </c>
     </row>
@@ -1882,31 +1882,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>158.23</v>
+        <v>298.39</v>
       </c>
       <c r="E41" t="n">
-        <v>139.87</v>
+        <v>208.74</v>
       </c>
       <c r="F41" t="n">
-        <v>11.65</v>
+        <v>10.93</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[858.92, 811.48, 1642.49]</t>
+          <t>[669.29, 2453.19, 713.44]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[936.86, 713.69, 1886.37]</t>
+          <t>[755.93, 2961.75, 744.45]</t>
         </is>
       </c>
     </row>
@@ -1918,31 +1918,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>431.03</v>
+        <v>495.67</v>
       </c>
       <c r="E42" t="n">
-        <v>392.58</v>
+        <v>381.18</v>
       </c>
       <c r="F42" t="n">
-        <v>49.76</v>
+        <v>27.81</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[233.41, 419.92, 475.49]</t>
+          <t>[777.01, 942.43, 621.62]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[463.04, 727.88, 1115.63]</t>
+          <t>[749.4, 1738.77, 941.21]</t>
         </is>
       </c>
     </row>
@@ -1954,31 +1954,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>405.58</v>
+        <v>617.78</v>
       </c>
       <c r="E43" t="n">
-        <v>380.25</v>
+        <v>584.99</v>
       </c>
       <c r="F43" t="n">
-        <v>41.04</v>
+        <v>40.92</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[454.28, 536.02, 568.76]</t>
+          <t>[941.38, 621.59, 847.2]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[727.88, 1115.63, 856.29]</t>
+          <t>[1738.77, 941.21, 1485.16]</t>
         </is>
       </c>
     </row>
@@ -1990,31 +1990,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>382.79</v>
+        <v>552.8200000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>358.11</v>
+        <v>526.16</v>
       </c>
       <c r="F44" t="n">
-        <v>36.36</v>
+        <v>30.85</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[566.34, 597.82, 632.18]</t>
+          <t>[649.67, 884.96, 2557.84]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[1115.63, 856.29, 898.75]</t>
+          <t>[941.21, 1485.16, 3244.57]</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>208.68</v>
+        <v>492.26</v>
       </c>
       <c r="E45" t="n">
-        <v>206.14</v>
+        <v>466.59</v>
       </c>
       <c r="F45" t="n">
-        <v>20.93</v>
+        <v>34.6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[627.69, 669.17, 1359.77]</t>
+          <t>[914.48, 2660.33, 271.89]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[856.29, 898.75, 1520.02]</t>
+          <t>[1485.16, 3244.57, 516.73]</t>
         </is>
       </c>
     </row>
@@ -2062,31 +2062,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>355.82</v>
+        <v>268.41</v>
       </c>
       <c r="E46" t="n">
-        <v>299.14</v>
+        <v>263.64</v>
       </c>
       <c r="F46" t="n">
-        <v>23.93</v>
+        <v>28.59</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[685.58, 1401.82, 838.34]</t>
+          <t>[2911.27, 300.88, 475.03]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[898.75, 1520.02, 1404.39]</t>
+          <t>[3244.57, 516.73, 716.8]</t>
         </is>
       </c>
     </row>
@@ -2098,31 +2098,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>319.5</v>
+        <v>298.19</v>
       </c>
       <c r="E47" t="n">
-        <v>216.39</v>
+        <v>284.08</v>
       </c>
       <c r="F47" t="n">
-        <v>15.33</v>
+        <v>37.35</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[1420.18, 860.11, 744.36]</t>
+          <t>[306.87, 486.14, 637.26]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[1520.02, 1404.39, 749.4]</t>
+          <t>[516.73, 716.8, 1048.98]</t>
         </is>
       </c>
     </row>
@@ -2134,31 +2134,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>563.54</v>
+        <v>267.64</v>
       </c>
       <c r="E48" t="n">
-        <v>454.81</v>
+        <v>251.01</v>
       </c>
       <c r="F48" t="n">
-        <v>28.93</v>
+        <v>28.41</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[868.82, 736.47, 922.84]</t>
+          <t>[502.81, 670.33, 672.09]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[1404.39, 749.4, 1738.77]</t>
+          <t>[716.8, 1048.98, 832.48]</t>
         </is>
       </c>
     </row>
@@ -2170,31 +2170,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>495.67</v>
+        <v>211.38</v>
       </c>
       <c r="E49" t="n">
-        <v>381.18</v>
+        <v>188</v>
       </c>
       <c r="F49" t="n">
-        <v>27.81</v>
+        <v>19.23</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[777.01, 942.43, 621.62]</t>
+          <t>[726.58, 733.11, 804.41]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[749.4, 1738.77, 941.21]</t>
+          <t>[1048.98, 832.48, 946.63]</t>
         </is>
       </c>
     </row>
@@ -2206,31 +2206,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>617.78</v>
+        <v>133.73</v>
       </c>
       <c r="E50" t="n">
-        <v>584.99</v>
+        <v>114.66</v>
       </c>
       <c r="F50" t="n">
-        <v>40.92</v>
+        <v>9.9</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[941.38, 621.59, 847.2]</t>
+          <t>[782.9, 862.13, 1625.8]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[1738.77, 941.21, 1485.16]</t>
+          <t>[832.48, 946.63, 1415.91]</t>
         </is>
       </c>
     </row>
@@ -2242,31 +2242,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>552.8200000000001</v>
+        <v>254.55</v>
       </c>
       <c r="E51" t="n">
-        <v>526.16</v>
+        <v>223.05</v>
       </c>
       <c r="F51" t="n">
-        <v>30.85</v>
+        <v>16.23</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[649.67, 884.96, 2557.84]</t>
+          <t>[848.24, 1596.81, 1137.21]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[941.21, 1485.16, 3244.57]</t>
+          <t>[946.63, 1415.91, 1527.06]</t>
         </is>
       </c>
     </row>
@@ -2278,19 +2278,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.23</v>
+        <v>0.87</v>
       </c>
       <c r="E52" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[0.0, 0.0, 1.5]</t>
         </is>
       </c>
     </row>
@@ -2316,19 +2316,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="E53" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.02]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.4]</t>
+          <t>[0.0, 1.5, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2354,19 +2354,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.24</v>
+        <v>1.01</v>
       </c>
       <c r="E54" t="n">
-        <v>0.17</v>
+        <v>0.8</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2375,12 +2375,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[0.01, 0.0, 0.01]</t>
+          <t>[0.0, 0.01, 0.0]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.1]</t>
+          <t>[1.5, 0.0, 0.9]</t>
         </is>
       </c>
     </row>
@@ -2392,31 +2392,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="E55" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="F55" t="n">
-        <v>98.69</v>
+        <v>0.51</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.03, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[0.4, 0.1, 0.3]</t>
+          <t>[0.0, 0.9, 0.6]</t>
         </is>
       </c>
     </row>
@@ -2428,19 +2430,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="E56" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2454,7 +2456,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[0.1, 0.3, 0.0]</t>
+          <t>[0.9, 0.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2466,19 +2468,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2492,7 +2494,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[0.3, 0.0, 0.0]</t>
+          <t>[0.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2506,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2525,7 +2527,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.01]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2542,19 +2544,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2568,7 +2570,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.5]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2580,19 +2582,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.86</v>
+        <v>2.89</v>
       </c>
       <c r="E60" t="n">
-        <v>0.51</v>
+        <v>1.67</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2601,12 +2603,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.02]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[0.0, 1.5, 0.0]</t>
+          <t>[0.0, 0.0, 5.0]</t>
         </is>
       </c>
     </row>
@@ -2618,19 +2620,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.01</v>
+        <v>4.51</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8</v>
+        <v>3.67</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2639,12 +2641,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[0.0, 0.01, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[1.5, 0.0, 0.9]</t>
+          <t>[0.0, 5.0, 6.0]</t>
         </is>
       </c>
     </row>
@@ -2656,31 +2658,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="E62" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="F62" t="n">
-        <v>22.94</v>
+        <v>28.08</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[0.52, 0.51, 0.94]</t>
+          <t>[1.26, 1.02, 0.96]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[0.7, 0.6, 1.3]</t>
+          <t>[2.0, 0.8, 0.8]</t>
         </is>
       </c>
     </row>
@@ -2692,31 +2694,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="E63" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="F63" t="n">
-        <v>16.56</v>
+        <v>27.87</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[0.52, 0.96, 0.77]</t>
+          <t>[1.03, 0.96, 0.81]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[0.6, 1.3, 0.7]</t>
+          <t>[0.8, 0.8, 0.6]</t>
         </is>
       </c>
     </row>
@@ -2728,31 +2730,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="E64" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F64" t="n">
-        <v>13.35</v>
+        <v>19.67</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[0.98, 0.78, 0.93]</t>
+          <t>[0.98, 0.82, 0.99]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[1.3, 0.7, 0.9]</t>
+          <t>[0.8, 0.6, 1.0]</t>
         </is>
       </c>
     </row>
@@ -2764,31 +2766,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F65" t="n">
-        <v>14.65</v>
+        <v>23.01</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[0.77, 0.92, 0.92]</t>
+          <t>[0.81, 1.0, 0.46]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[0.7, 0.9, 0.7]</t>
+          <t>[0.6, 1.0, 0.7]</t>
         </is>
       </c>
     </row>
@@ -2800,31 +2802,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="E66" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="F66" t="n">
-        <v>13.87</v>
+        <v>24.42</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[0.94, 0.93, 1.15]</t>
+          <t>[0.99, 0.46, 0.44]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[0.9, 0.7, 1.1]</t>
+          <t>[1.0, 0.7, 0.7]</t>
         </is>
       </c>
     </row>
@@ -2836,31 +2838,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="E67" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="F67" t="n">
-        <v>24.96</v>
+        <v>34.63</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[0.94, 1.16, 1.29]</t>
+          <t>[0.46, 0.44, 0.81]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[0.7, 1.1, 2.0]</t>
+          <t>[0.7, 0.7, 1.2]</t>
         </is>
       </c>
     </row>
@@ -2872,31 +2874,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="E68" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="F68" t="n">
-        <v>22.33</v>
+        <v>29.3</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[1.14, 1.28, 1.02]</t>
+          <t>[0.44, 0.83, 0.63]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[1.1, 2.0, 0.8]</t>
+          <t>[0.7, 1.2, 0.8]</t>
         </is>
       </c>
     </row>
@@ -2908,31 +2910,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="E69" t="n">
-        <v>0.37</v>
+        <v>0.2</v>
       </c>
       <c r="F69" t="n">
-        <v>28.08</v>
+        <v>20.21</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[1.26, 1.02, 0.96]</t>
+          <t>[0.86, 0.65, 0.78]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[2.0, 0.8, 0.8]</t>
+          <t>[1.2, 0.8, 0.9]</t>
         </is>
       </c>
     </row>
@@ -2944,31 +2946,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="F70" t="n">
-        <v>27.87</v>
+        <v>13.44</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[1.03, 0.96, 0.81]</t>
+          <t>[0.65, 0.78, 0.76]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[0.8, 0.8, 0.6]</t>
+          <t>[0.8, 0.9, 0.7]</t>
         </is>
       </c>
     </row>
@@ -2980,31 +2982,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F71" t="n">
-        <v>19.67</v>
+        <v>10.93</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[0.98, 0.82, 0.99]</t>
+          <t>[0.8, 0.78, 0.99]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[0.8, 0.6, 1.0]</t>
+          <t>[0.9, 0.7, 1.1]</t>
         </is>
       </c>
     </row>
@@ -3016,31 +3018,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>22.98</v>
+        <v>8.1</v>
       </c>
       <c r="E72" t="n">
-        <v>18.67</v>
+        <v>6.49</v>
       </c>
       <c r="F72" t="n">
-        <v>19.01</v>
+        <v>13.11</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[83.31, 60.15, 58.94]</t>
+          <t>[48.33, 55.0, 64.92]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[118.5, 78.6, 61.3]</t>
+          <t>[43.3, 53.6, 51.9]</t>
         </is>
       </c>
     </row>
@@ -3052,31 +3054,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.64</v>
+        <v>11.75</v>
       </c>
       <c r="E73" t="n">
-        <v>7.88</v>
+        <v>10.09</v>
       </c>
       <c r="F73" t="n">
-        <v>11.5</v>
+        <v>15.88</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[61.01, 61.91, 54.45]</t>
+          <t>[55.28, 65.13, 65.46]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[78.6, 61.3, 49.0]</t>
+          <t>[53.6, 51.9, 80.83]</t>
         </is>
       </c>
     </row>
@@ -3088,31 +3090,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5.98</v>
+        <v>49.85</v>
       </c>
       <c r="E74" t="n">
-        <v>5.71</v>
+        <v>37.51</v>
       </c>
       <c r="F74" t="n">
-        <v>11.25</v>
+        <v>28.05</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[64.58, 56.51, 54.84]</t>
+          <t>[65.25, 65.58, 128.19]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[61.3, 49.0, 48.5]</t>
+          <t>[51.9, 80.83, 212.13]</t>
         </is>
       </c>
     </row>
@@ -3124,31 +3126,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>96.03</v>
+        <v>49.08</v>
       </c>
       <c r="E75" t="n">
-        <v>59.79</v>
+        <v>35.01</v>
       </c>
       <c r="F75" t="n">
-        <v>34.72</v>
+        <v>21.31</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[56.27, 54.55, 50.06]</t>
+          <t>[65.98, 128.69, 101.65]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[49.0, 48.5, 216.12]</t>
+          <t>[80.83, 212.13, 108.39]</t>
         </is>
       </c>
     </row>
@@ -3160,31 +3162,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>96.26000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="E76" t="n">
-        <v>62.43</v>
+        <v>31.63</v>
       </c>
       <c r="F76" t="n">
-        <v>41.53</v>
+        <v>17.1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[54.58, 50.21, 58.71]</t>
+          <t>[128.15, 101.82, 72.38]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[48.5, 216.12, 43.4]</t>
+          <t>[212.13, 108.39, 76.72]</t>
         </is>
       </c>
     </row>
@@ -3196,31 +3198,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>96.29000000000001</v>
+        <v>4.52</v>
       </c>
       <c r="E77" t="n">
-        <v>61.88</v>
+        <v>3.91</v>
       </c>
       <c r="F77" t="n">
-        <v>40.67</v>
+        <v>4.34</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[50.07, 58.22, 48.08]</t>
+          <t>[101.63, 72.99, 62.33]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[216.12, 43.4, 43.3]</t>
+          <t>[108.39, 76.72, 63.56]</t>
         </is>
       </c>
     </row>
@@ -3232,31 +3234,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>9.24</v>
+        <v>2.99</v>
       </c>
       <c r="E78" t="n">
-        <v>7.72</v>
+        <v>2.71</v>
       </c>
       <c r="F78" t="n">
-        <v>17.43</v>
+        <v>4.47</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[58.02, 49.28, 56.17]</t>
+          <t>[73.15, 62.65, 53.44]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[43.4, 43.3, 53.6]</t>
+          <t>[76.72, 63.56, 49.8]</t>
         </is>
       </c>
     </row>
@@ -3268,31 +3270,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8.1</v>
+        <v>3.95</v>
       </c>
       <c r="E79" t="n">
-        <v>6.49</v>
+        <v>3.47</v>
       </c>
       <c r="F79" t="n">
-        <v>13.11</v>
+        <v>6.95</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[48.33, 55.0, 64.92]</t>
+          <t>[62.39, 53.26, 53.79]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[43.3, 53.6, 51.9]</t>
+          <t>[63.56, 49.8, 48.0]</t>
         </is>
       </c>
     </row>
@@ -3304,31 +3306,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.75</v>
+        <v>4.14</v>
       </c>
       <c r="E80" t="n">
-        <v>10.09</v>
+        <v>3.32</v>
       </c>
       <c r="F80" t="n">
-        <v>15.88</v>
+        <v>6.79</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[55.28, 65.13, 65.46]</t>
+          <t>[53.57, 54.1, 85.02]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[53.6, 51.9, 80.83]</t>
+          <t>[49.8, 48.0, 85.1]</t>
         </is>
       </c>
     </row>
@@ -3340,31 +3342,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>49.85</v>
+        <v>41.91</v>
       </c>
       <c r="E81" t="n">
-        <v>37.51</v>
+        <v>26.27</v>
       </c>
       <c r="F81" t="n">
-        <v>28.05</v>
+        <v>23.12</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[65.25, 65.58, 128.19]</t>
+          <t>[53.76, 84.4, 55.65]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[51.9, 80.83, 212.13]</t>
+          <t>[48.0, 85.1, 128.01]</t>
         </is>
       </c>
     </row>
@@ -3376,31 +3378,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>87.59999999999999</v>
+        <v>219.11</v>
       </c>
       <c r="E82" t="n">
-        <v>57.77</v>
+        <v>202</v>
       </c>
       <c r="F82" t="n">
-        <v>3.02</v>
+        <v>7.33</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[1740.92, 1810.99, 2116.62]</t>
+          <t>[2482.08, 2885.77, 3392.9]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[1890.85, 1811.02, 2093.26]</t>
+          <t>[2216.19, 2803.71, 3650.97]</t>
         </is>
       </c>
     </row>
@@ -3412,31 +3414,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>148.79</v>
+        <v>211.83</v>
       </c>
       <c r="E83" t="n">
-        <v>102.54</v>
+        <v>186.74</v>
       </c>
       <c r="F83" t="n">
-        <v>4.88</v>
+        <v>5.2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[1820.47, 2137.77, 1862.35]</t>
+          <t>[2857.54, 3355.93, 3571.1]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[1811.02, 2093.26, 2116.01]</t>
+          <t>[2803.71, 3650.97, 3782.45]</t>
         </is>
       </c>
     </row>
@@ -3448,31 +3450,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>340.08</v>
+        <v>412.73</v>
       </c>
       <c r="E84" t="n">
-        <v>274.57</v>
+        <v>374.75</v>
       </c>
       <c r="F84" t="n">
-        <v>11.37</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[2127.74, 1852.41, 2101.95]</t>
+          <t>[3353.74, 3569.82, 4081.11]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[2093.26, 2116.01, 2627.58]</t>
+          <t>[3650.97, 3782.45, 4695.5]</t>
         </is>
       </c>
     </row>
@@ -3484,31 +3486,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>479.75</v>
+        <v>368.02</v>
       </c>
       <c r="E85" t="n">
-        <v>459.18</v>
+        <v>309.49</v>
       </c>
       <c r="F85" t="n">
-        <v>14.92</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[1850.65, 2099.78, 4231.33]</t>
+          <t>[3586.89, 4106.0, 1737.06]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[2116.01, 2627.58, 4815.7]</t>
+          <t>[3782.45, 4695.5, 1880.47]</t>
         </is>
       </c>
     </row>
@@ -3520,31 +3522,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>424.11</v>
+        <v>342.85</v>
       </c>
       <c r="E86" t="n">
-        <v>354.21</v>
+        <v>261.98</v>
       </c>
       <c r="F86" t="n">
-        <v>10.44</v>
+        <v>7.9</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[2122.04, 4283.31, 2468.22]</t>
+          <t>[4122.45, 1745.77, 1728.08]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[2627.58, 4815.7, 2443.5]</t>
+          <t>[4695.5, 1880.47, 1806.25]</t>
         </is>
       </c>
     </row>
@@ -3556,31 +3558,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>296.85</v>
+        <v>94.77</v>
       </c>
       <c r="E87" t="n">
-        <v>257.98</v>
+        <v>91.12</v>
       </c>
       <c r="F87" t="n">
-        <v>7.93</v>
+        <v>4.69</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[4373.38, 2526.49, 2464.84]</t>
+          <t>[1764.78, 1751.18, 2006.89]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[4815.7, 2443.5, 2216.19]</t>
+          <t>[1880.47, 1806.25, 2109.5]</t>
         </is>
       </c>
     </row>
@@ -3592,31 +3594,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>186.38</v>
+        <v>167.96</v>
       </c>
       <c r="E88" t="n">
-        <v>167.41</v>
+        <v>137.8</v>
       </c>
       <c r="F88" t="n">
-        <v>7.06</v>
+        <v>6.68</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[2558.01, 2499.33, 2908.29]</t>
+          <t>[1756.19, 2017.6, 1830.66]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[2443.5, 2216.19, 2803.71]</t>
+          <t>[1806.25, 2109.5, 2102.1]</t>
         </is>
       </c>
     </row>
@@ -3628,31 +3630,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>219.11</v>
+        <v>235.95</v>
       </c>
       <c r="E89" t="n">
-        <v>202</v>
+        <v>216.2</v>
       </c>
       <c r="F89" t="n">
-        <v>7.33</v>
+        <v>9.59</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[2482.08, 2885.77, 3392.9]</t>
+          <t>[2025.26, 1838.22, 2154.92]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[2216.19, 2803.71, 3650.97]</t>
+          <t>[2109.5, 2102.1, 2455.4]</t>
         </is>
       </c>
     </row>
@@ -3664,31 +3666,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>211.83</v>
+        <v>376.72</v>
       </c>
       <c r="E90" t="n">
-        <v>186.74</v>
+        <v>354.81</v>
       </c>
       <c r="F90" t="n">
-        <v>5.2</v>
+        <v>11.48</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[2857.54, 3355.93, 3571.1]</t>
+          <t>[1853.02, 2172.85, 4271.21]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[2803.71, 3650.97, 3782.45]</t>
+          <t>[2102.1, 2455.4, 4804.0]</t>
         </is>
       </c>
     </row>
@@ -3700,31 +3702,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>412.73</v>
+        <v>275.64</v>
       </c>
       <c r="E91" t="n">
-        <v>374.75</v>
+        <v>223.02</v>
       </c>
       <c r="F91" t="n">
-        <v>8.949999999999999</v>
+        <v>6.31</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[3353.74, 3569.82, 4081.11]</t>
+          <t>[2227.08, 4385.29, 2452.88]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[3650.97, 3782.45, 4695.5]</t>
+          <t>[2455.4, 4804.0, 2430.85]</t>
         </is>
       </c>
     </row>
@@ -3736,31 +3738,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>69.90000000000001</v>
+        <v>146.97</v>
       </c>
       <c r="E92" t="n">
-        <v>59.96</v>
+        <v>108.34</v>
       </c>
       <c r="F92" t="n">
-        <v>8.67</v>
+        <v>6.15</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[568.3, 497.43, 974.2]</t>
+          <t>[1538.36, 1518.31, 1672.08]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[586.05, 603.01, 1030.75]</t>
+          <t>[1783.24, 1506.79, 1740.69]</t>
         </is>
       </c>
     </row>
@@ -3772,31 +3774,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>80.59999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="E93" t="n">
-        <v>77.59999999999999</v>
+        <v>25.35</v>
       </c>
       <c r="F93" t="n">
-        <v>9.34</v>
+        <v>1.57</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[499.21, 980.23, 1407.19]</t>
+          <t>[1544.02, 1702.49, 1660.71]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[603.01, 1030.75, 1328.7]</t>
+          <t>[1506.79, 1740.69, 1660.1]</t>
         </is>
       </c>
     </row>
@@ -3808,31 +3810,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>70.38</v>
+        <v>154.5</v>
       </c>
       <c r="E94" t="n">
-        <v>53.33</v>
+        <v>104.8</v>
       </c>
       <c r="F94" t="n">
-        <v>4.09</v>
+        <v>3.78</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[1009.27, 1446.97, 1559.63]</t>
+          <t>[1696.19, 1654.01, 2875.77]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[1030.75, 1328.7, 1579.88]</t>
+          <t>[1740.69, 1660.1, 3139.58]</t>
         </is>
       </c>
     </row>
@@ -3844,31 +3846,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>173.07</v>
+        <v>152.77</v>
       </c>
       <c r="E95" t="n">
-        <v>137.36</v>
+        <v>107.02</v>
       </c>
       <c r="F95" t="n">
-        <v>7.59</v>
+        <v>6.29</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[1446.2, 1560.39, 2440.47]</t>
+          <t>[1660.86, 2882.68, 532.27]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[1328.7, 1579.88, 2165.38]</t>
+          <t>[1660.1, 3139.58, 595.67]</t>
         </is>
       </c>
     </row>
@@ -3880,31 +3882,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>160.57</v>
+        <v>170.09</v>
       </c>
       <c r="E96" t="n">
-        <v>127.28</v>
+        <v>149.49</v>
       </c>
       <c r="F96" t="n">
-        <v>6.74</v>
+        <v>13.02</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[1553.11, 2425.38, 1365.71]</t>
+          <t>[2881.65, 532.89, 501.61]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[1579.88, 2165.38, 1460.76]</t>
+          <t>[3139.58, 595.67, 629.36]</t>
         </is>
       </c>
     </row>
@@ -3916,31 +3918,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>206.79</v>
+        <v>104.81</v>
       </c>
       <c r="E97" t="n">
-        <v>194.8</v>
+        <v>100.6</v>
       </c>
       <c r="F97" t="n">
-        <v>10.49</v>
+        <v>13.5</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[2416.84, 1363.68, 1547.39]</t>
+          <t>[536.56, 505.26, 974.54]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[2165.38, 1460.76, 1783.24]</t>
+          <t>[595.67, 629.36, 1093.13]</t>
         </is>
       </c>
     </row>
@@ -3952,31 +3954,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>160.41</v>
+        <v>102.27</v>
       </c>
       <c r="E98" t="n">
-        <v>122.8</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>7.36</v>
+        <v>11.43</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[1348.62, 1529.05, 1508.87]</t>
+          <t>[508.51, 981.95, 1414.43]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[1460.76, 1783.24, 1506.79]</t>
+          <t>[629.36, 1093.13, 1348.0]</t>
         </is>
       </c>
     </row>
@@ -3988,31 +3990,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>146.97</v>
+        <v>80.69</v>
       </c>
       <c r="E99" t="n">
-        <v>108.34</v>
+        <v>76.48</v>
       </c>
       <c r="F99" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[1538.36, 1518.31, 1672.08]</t>
+          <t>[1000.42, 1444.57, 1570.56]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[1783.24, 1506.79, 1740.69]</t>
+          <t>[1093.13, 1348.0, 1610.72]</t>
         </is>
       </c>
     </row>
@@ -4024,31 +4026,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>30.8</v>
+        <v>101.45</v>
       </c>
       <c r="E100" t="n">
-        <v>25.35</v>
+        <v>90.88</v>
       </c>
       <c r="F100" t="n">
-        <v>1.57</v>
+        <v>5.27</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[1544.02, 1702.49, 1660.71]</t>
+          <t>[1453.77, 1580.97, 2375.61]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[1506.79, 1740.69, 1660.1]</t>
+          <t>[1348.0, 1610.72, 2238.47]</t>
         </is>
       </c>
     </row>
@@ -4060,31 +4062,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>154.5</v>
+        <v>100.86</v>
       </c>
       <c r="E101" t="n">
-        <v>104.8</v>
+        <v>93.22</v>
       </c>
       <c r="F101" t="n">
-        <v>3.78</v>
+        <v>5.17</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[1696.19, 1654.01, 2875.77]</t>
+          <t>[1571.85, 2361.72, 1430.89]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[1740.69, 1660.1, 3139.58]</t>
+          <t>[1610.72, 2238.47, 1548.44]</t>
         </is>
       </c>
     </row>
@@ -4096,31 +4098,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>146.22</v>
+        <v>404.46</v>
       </c>
       <c r="E102" t="n">
-        <v>140.21</v>
+        <v>325.43</v>
       </c>
       <c r="F102" t="n">
-        <v>25.65</v>
+        <v>23.54</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[346.98, 284.07, 666.79]</t>
+          <t>[663.18, 1894.6, 590.05]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[428.9, 459.13, 830.45]</t>
+          <t>[884.19, 2552.15, 492.32]</t>
         </is>
       </c>
     </row>
@@ -4132,31 +4134,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>135.77</v>
+        <v>405.28</v>
       </c>
       <c r="E103" t="n">
-        <v>130.56</v>
+        <v>345.15</v>
       </c>
       <c r="F103" t="n">
-        <v>25.2</v>
+        <v>24.69</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[289.52, 688.83, 291.83]</t>
+          <t>[1928.2, 601.17, 797.0]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[459.13, 830.45, 372.29]</t>
+          <t>[2552.15, 492.32, 1099.66]</t>
         </is>
       </c>
     </row>
@@ -4168,31 +4170,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>165.79</v>
+        <v>306.99</v>
       </c>
       <c r="E104" t="n">
-        <v>135.97</v>
+        <v>280.85</v>
       </c>
       <c r="F104" t="n">
-        <v>16.24</v>
+        <v>23.23</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[747.57, 316.45, 864.74]</t>
+          <t>[635.29, 843.63, 2108.42]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[830.45, 372.29, 1133.94]</t>
+          <t>[492.32, 1099.66, 2551.96]</t>
         </is>
       </c>
     </row>
@@ -4204,31 +4206,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>370.42</v>
+        <v>313.64</v>
       </c>
       <c r="E105" t="n">
-        <v>298.89</v>
+        <v>247.65</v>
       </c>
       <c r="F105" t="n">
-        <v>21.84</v>
+        <v>14.5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[319.53, 874.41, 1468.28]</t>
+          <t>[831.13, 2079.73, 378.8]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[372.29, 1133.94, 2052.66]</t>
+          <t>[1099.66, 2551.96, 381.0]</t>
         </is>
       </c>
     </row>
@@ -4240,31 +4242,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>363.79</v>
+        <v>222.55</v>
       </c>
       <c r="E106" t="n">
-        <v>303.8</v>
+        <v>152.62</v>
       </c>
       <c r="F106" t="n">
-        <v>22.09</v>
+        <v>11.84</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[880.92, 1482.34, 456.82]</t>
+          <t>[2171.74, 397.51, 313.91]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[1133.94, 2052.66, 544.87]</t>
+          <t>[2551.96, 381.0, 375.04]</t>
         </is>
       </c>
     </row>
@@ -4276,31 +4278,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>348.51</v>
+        <v>45.19</v>
       </c>
       <c r="E107" t="n">
-        <v>292.37</v>
+        <v>44.18</v>
       </c>
       <c r="F107" t="n">
-        <v>23.32</v>
+        <v>9.09</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[1514.03, 467.76, 622.81]</t>
+          <t>[412.34, 327.82, 783.56]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[2052.66, 544.87, 884.19]</t>
+          <t>[381.0, 375.04, 837.54]</t>
         </is>
       </c>
     </row>
@@ -4312,31 +4314,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>439.21</v>
+        <v>40.41</v>
       </c>
       <c r="E108" t="n">
-        <v>341.43</v>
+        <v>36.43</v>
       </c>
       <c r="F108" t="n">
-        <v>22.41</v>
+        <v>7.2</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[481.14, 641.95, 1833.84]</t>
+          <t>[329.99, 785.35, 345.69]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[544.87, 884.19, 2552.15]</t>
+          <t>[375.04, 837.54, 357.73]</t>
         </is>
       </c>
     </row>
@@ -4348,31 +4350,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>404.46</v>
+        <v>64.17</v>
       </c>
       <c r="E109" t="n">
-        <v>325.43</v>
+        <v>46.6</v>
       </c>
       <c r="F109" t="n">
-        <v>23.54</v>
+        <v>4.58</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[663.18, 1894.6, 590.05]</t>
+          <t>[806.45, 355.7, 1021.26]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[884.19, 2552.15, 492.32]</t>
+          <t>[837.54, 357.73, 1127.95]</t>
         </is>
       </c>
     </row>
@@ -4384,31 +4386,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>405.28</v>
+        <v>185.97</v>
       </c>
       <c r="E110" t="n">
-        <v>345.15</v>
+        <v>133.65</v>
       </c>
       <c r="F110" t="n">
-        <v>24.69</v>
+        <v>7.9</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[1928.2, 601.17, 797.0]</t>
+          <t>[362.77, 1042.61, 1800.07]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[2552.15, 492.32, 1099.66]</t>
+          <t>[357.73, 1127.95, 2110.63]</t>
         </is>
       </c>
     </row>
@@ -4420,31 +4422,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>306.99</v>
+        <v>175.42</v>
       </c>
       <c r="E111" t="n">
-        <v>280.85</v>
+        <v>131.25</v>
       </c>
       <c r="F111" t="n">
-        <v>23.23</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[635.29, 843.63, 2108.42]</t>
+          <t>[1052.45, 1817.4, 543.05]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[492.32, 1099.66, 2551.96]</t>
+          <t>[1127.95, 2110.63, 518.05]</t>
         </is>
       </c>
     </row>
@@ -4456,31 +4458,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>37.53</v>
+        <v>10.78</v>
       </c>
       <c r="E112" t="n">
-        <v>31.9</v>
+        <v>7.87</v>
       </c>
       <c r="F112" t="n">
-        <v>13.67</v>
+        <v>5.69</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>[256.47, 121.81, 159.72]</t>
+          <t>[118.53, 155.56, 138.86]</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>[315.08, 133.21, 185.42]</t>
+          <t>[136.33, 155.72, 144.52]</t>
         </is>
       </c>
     </row>
@@ -4492,31 +4494,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>114.11</v>
+        <v>7.82</v>
       </c>
       <c r="E113" t="n">
-        <v>75.59</v>
+        <v>6.11</v>
       </c>
       <c r="F113" t="n">
-        <v>10.87</v>
+        <v>2.23</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>[123.91, 164.23, 1185.1]</t>
+          <t>[157.11, 140.39, 447.75]</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>[133.21, 185.42, 1381.39]</t>
+          <t>[155.72, 144.52, 434.93]</t>
         </is>
       </c>
     </row>
@@ -4528,31 +4530,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>110.42</v>
+        <v>53.19</v>
       </c>
       <c r="E114" t="n">
-        <v>78.51000000000001</v>
+        <v>35.86</v>
       </c>
       <c r="F114" t="n">
-        <v>17.68</v>
+        <v>8.83</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>[165.6, 1193.16, 68.17]</t>
+          <t>[140.17, 446.93, 531.72]</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[185.42, 1381.39, 95.65]</t>
+          <t>[144.52, 434.93, 440.47]</t>
         </is>
       </c>
     </row>
@@ -4564,31 +4566,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>117.14</v>
+        <v>71</v>
       </c>
       <c r="E115" t="n">
-        <v>100.16</v>
+        <v>61.57</v>
       </c>
       <c r="F115" t="n">
-        <v>31.5</v>
+        <v>16.02</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>[1206.03, 69.05, 83.9]</t>
+          <t>[446.86, 532.15, 249.78]</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[1381.39, 95.65, 182.41]</t>
+          <t>[434.93, 440.47, 330.86]</t>
         </is>
       </c>
     </row>
@@ -4600,31 +4602,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>65.95</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="E116" t="n">
-        <v>58.95</v>
+        <v>66.23</v>
       </c>
       <c r="F116" t="n">
-        <v>36.88</v>
+        <v>21.31</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[69.55, 84.64, 125.04]</t>
+          <t>[532.13, 250.54, 115.15]</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[95.65, 182.41, 178.03]</t>
+          <t>[440.47, 330.86, 141.87]</t>
         </is>
       </c>
     </row>
@@ -4636,31 +4638,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>63.78</v>
+        <v>51.84</v>
       </c>
       <c r="E117" t="n">
-        <v>57.57</v>
+        <v>44.43</v>
       </c>
       <c r="F117" t="n">
-        <v>33.61</v>
+        <v>19.12</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>[87.55, 129.76, 106.75]</t>
+          <t>[248.69, 114.68, 155.14]</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[182.41, 178.03, 136.33]</t>
+          <t>[330.86, 141.87, 179.06]</t>
         </is>
       </c>
     </row>
@@ -4672,31 +4674,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>24.87</v>
+        <v>134.22</v>
       </c>
       <c r="E118" t="n">
-        <v>20.45</v>
+        <v>91.47</v>
       </c>
       <c r="F118" t="n">
-        <v>12.73</v>
+        <v>14.76</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>[140.12, 116.13, 152.48]</t>
+          <t>[117.17, 159.69, 1203.65]</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[178.03, 136.33, 155.72]</t>
+          <t>[141.87, 179.06, 1433.99]</t>
         </is>
       </c>
     </row>
@@ -4708,31 +4710,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.78</v>
+        <v>117.35</v>
       </c>
       <c r="E119" t="n">
-        <v>7.87</v>
+        <v>92.53</v>
       </c>
       <c r="F119" t="n">
-        <v>5.69</v>
+        <v>23.78</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>[118.53, 155.56, 138.86]</t>
+          <t>[164.91, 1245.64, 74.21]</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[136.33, 155.72, 144.52]</t>
+          <t>[179.06, 1433.99, 149.31]</t>
         </is>
       </c>
     </row>
@@ -4744,31 +4746,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>7.82</v>
+        <v>100.03</v>
       </c>
       <c r="E120" t="n">
-        <v>6.11</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>2.23</v>
+        <v>27.49</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[157.11, 140.39, 447.75]</t>
+          <t>[1279.84, 76.37, 103.31]</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[155.72, 144.52, 434.93]</t>
+          <t>[1433.99, 149.31, 133.92]</t>
         </is>
       </c>
     </row>
@@ -4780,31 +4782,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>53.19</v>
+        <v>43.93</v>
       </c>
       <c r="E121" t="n">
-        <v>35.86</v>
+        <v>35.58</v>
       </c>
       <c r="F121" t="n">
-        <v>8.83</v>
+        <v>24.47</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[140.17, 446.93, 531.72]</t>
+          <t>[78.78, 106.87, 143.93]</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[144.52, 434.93, 440.47]</t>
+          <t>[149.31, 133.92, 153.09]</t>
         </is>
       </c>
     </row>
@@ -4816,31 +4818,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>70.88</v>
+        <v>33.73</v>
       </c>
       <c r="E122" t="n">
-        <v>70.86</v>
+        <v>29.21</v>
       </c>
       <c r="F122" t="n">
-        <v>14.63</v>
+        <v>4.64</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[462.61, 401.52, 381.74]</t>
+          <t>[675.4, 572.75, 543.36]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[535.11, 473.04, 450.3]</t>
+          <t>[709.2, 579.41, 590.55]</t>
         </is>
       </c>
     </row>
@@ -4852,31 +4854,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>84.11</v>
+        <v>49.91</v>
       </c>
       <c r="E123" t="n">
-        <v>80.67</v>
+        <v>40.93</v>
       </c>
       <c r="F123" t="n">
-        <v>16.71</v>
+        <v>7.24</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[406.06, 389.41, 394.46]</t>
+          <t>[574.43, 547.6, 476.02]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[473.04, 450.3, 508.6]</t>
+          <t>[579.41, 590.55, 550.88]</t>
         </is>
       </c>
     </row>
@@ -4888,31 +4890,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>84.29000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>81.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="F124" t="n">
-        <v>15.67</v>
+        <v>13.06</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[397.33, 402.87, 506.19]</t>
+          <t>[547.1, 476.96, 644.21]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[450.3, 508.6, 591.8]</t>
+          <t>[590.55, 550.88, 544.11]</t>
         </is>
       </c>
     </row>
@@ -4924,31 +4926,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>75.08</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E125" t="n">
-        <v>70.55</v>
+        <v>88.62</v>
       </c>
       <c r="F125" t="n">
-        <v>12.75</v>
+        <v>16.34</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[409.23, 516.5, 580.26]</t>
+          <t>[476.97, 645.85, 443.59]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[508.6, 591.8, 617.25]</t>
+          <t>[550.88, 544.11, 533.78]</t>
         </is>
       </c>
     </row>
@@ -4960,31 +4962,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>127.13</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>99.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>24.81</v>
+        <v>15.98</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[525.53, 592.32, 560.64]</t>
+          <t>[653.78, 449.4, 417.47]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[591.8, 617.25, 352.14]</t>
+          <t>[544.11, 533.78, 474.22]</t>
         </is>
       </c>
     </row>
@@ -4996,31 +4998,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>124.67</v>
+        <v>72.33</v>
       </c>
       <c r="E127" t="n">
-        <v>80.2</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="F127" t="n">
-        <v>21.68</v>
+        <v>14.63</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[599.12, 567.18, 701.76]</t>
+          <t>[444.89, 411.25, 381.41]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[617.25, 352.14, 709.2]</t>
+          <t>[533.78, 474.22, 443.29]</t>
         </is>
       </c>
     </row>
@@ -5032,31 +5034,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>125.69</v>
+        <v>68.67</v>
       </c>
       <c r="E128" t="n">
-        <v>80.23</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>21.84</v>
+        <v>17.69</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[569.02, 703.39, 597.41]</t>
+          <t>[416.43, 387.76, 397.7]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[352.14, 709.2, 579.41]</t>
+          <t>[474.22, 443.29, 309.81]</t>
         </is>
       </c>
     </row>
@@ -5068,31 +5070,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>33.73</v>
+        <v>89.95</v>
       </c>
       <c r="E129" t="n">
-        <v>29.21</v>
+        <v>86.06</v>
       </c>
       <c r="F129" t="n">
-        <v>4.64</v>
+        <v>19.9</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[675.4, 572.75, 543.36]</t>
+          <t>[392.15, 402.79, 514.2]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[709.2, 579.41, 590.55]</t>
+          <t>[443.29, 309.81, 628.26]</t>
         </is>
       </c>
     </row>
@@ -5104,31 +5106,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>49.91</v>
+        <v>88.33</v>
       </c>
       <c r="E130" t="n">
-        <v>40.93</v>
+        <v>84.36</v>
       </c>
       <c r="F130" t="n">
-        <v>7.24</v>
+        <v>19.24</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[574.43, 547.6, 476.02]</t>
+          <t>[407.38, 520.55, 574.49]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[579.41, 590.55, 550.88]</t>
+          <t>[309.81, 628.26, 526.68]</t>
         </is>
       </c>
     </row>
@@ -5140,31 +5142,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>76.09999999999999</v>
+        <v>154.68</v>
       </c>
       <c r="E131" t="n">
-        <v>72.48999999999999</v>
+        <v>130.23</v>
       </c>
       <c r="F131" t="n">
-        <v>13.06</v>
+        <v>40.01</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[547.1, 476.96, 644.21]</t>
+          <t>[508.01, 560.05, 487.8]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[590.55, 550.88, 544.11]</t>
+          <t>[628.26, 526.68, 250.73]</t>
         </is>
       </c>
     </row>
@@ -5176,31 +5178,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9.99</v>
+        <v>33.2</v>
       </c>
       <c r="E132" t="n">
-        <v>9.34</v>
+        <v>25.81</v>
       </c>
       <c r="F132" t="n">
-        <v>5.98</v>
+        <v>8.57</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[183.56, 183.97, 101.87]</t>
+          <t>[227.52, 442.5, 253.07]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[169.4, 192.02, 107.68]</t>
+          <t>[215.64, 452.73, 308.4]</t>
         </is>
       </c>
     </row>
@@ -5212,31 +5214,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>9.17</v>
+        <v>29.56</v>
       </c>
       <c r="E133" t="n">
-        <v>9.17</v>
+        <v>21.49</v>
       </c>
       <c r="F133" t="n">
-        <v>8.18</v>
+        <v>6.59</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[182.69, 99.0, 91.1]</t>
+          <t>[440.83, 258.69, 274.74]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>[192.02, 107.68, 81.6]</t>
+          <t>[452.73, 308.4, 277.6]</t>
         </is>
       </c>
     </row>
@@ -5248,31 +5250,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>9.359999999999999</v>
+        <v>35.96</v>
       </c>
       <c r="E134" t="n">
-        <v>9.31</v>
+        <v>31.88</v>
       </c>
       <c r="F134" t="n">
-        <v>8.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[99.74, 91.08, 149.94]</t>
+          <t>[270.89, 268.32, 302.36]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[107.68, 81.6, 139.45]</t>
+          <t>[308.4, 277.6, 351.2]</t>
         </is>
       </c>
     </row>
@@ -5284,31 +5286,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>12.93</v>
+        <v>26.5</v>
       </c>
       <c r="E135" t="n">
-        <v>12.36</v>
+        <v>19.19</v>
       </c>
       <c r="F135" t="n">
-        <v>8.52</v>
+        <v>6.64</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[90.28, 150.27, 263.22]</t>
+          <t>[273.53, 306.3, 160.13]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>[81.6, 139.45, 245.63]</t>
+          <t>[277.6, 351.2, 151.54]</t>
         </is>
       </c>
     </row>
@@ -5320,31 +5322,31 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.95</v>
+        <v>27.58</v>
       </c>
       <c r="E136" t="n">
-        <v>10.21</v>
+        <v>22.03</v>
       </c>
       <c r="F136" t="n">
-        <v>5.46</v>
+        <v>8.76</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[151.61, 262.28, 211.8]</t>
+          <t>[305.87, 159.53, 170.31]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>[139.45, 245.63, 209.97]</t>
+          <t>[351.2, 151.54, 157.54]</t>
         </is>
       </c>
     </row>
@@ -5356,31 +5358,31 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>12.7</v>
+        <v>21.11</v>
       </c>
       <c r="E137" t="n">
-        <v>10.36</v>
+        <v>18.71</v>
       </c>
       <c r="F137" t="n">
-        <v>4.45</v>
+        <v>13.32</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[264.49, 210.91, 226.92]</t>
+          <t>[161.4, 171.48, 99.02]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>[245.63, 209.97, 215.64]</t>
+          <t>[151.54, 157.54, 131.34]</t>
         </is>
       </c>
     </row>
@@ -5392,31 +5394,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8.390000000000001</v>
+        <v>27.47</v>
       </c>
       <c r="E138" t="n">
-        <v>6.98</v>
+        <v>25.95</v>
       </c>
       <c r="F138" t="n">
-        <v>2.66</v>
+        <v>31.87</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[208.81, 228.18, 445.5]</t>
+          <t>[170.79, 98.54, 82.94]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>[209.97, 215.64, 452.73]</t>
+          <t>[157.54, 131.34, 51.12]</t>
         </is>
       </c>
     </row>
@@ -5428,31 +5430,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>33.2</v>
+        <v>27.45</v>
       </c>
       <c r="E139" t="n">
-        <v>25.81</v>
+        <v>25.8</v>
       </c>
       <c r="F139" t="n">
-        <v>8.57</v>
+        <v>32.35</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[227.52, 442.5, 253.07]</t>
+          <t>[98.47, 83.09, 144.96]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>[215.64, 452.73, 308.4]</t>
+          <t>[131.34, 51.12, 132.39]</t>
         </is>
       </c>
     </row>
@@ -5464,31 +5466,31 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>29.56</v>
+        <v>30.15</v>
       </c>
       <c r="E140" t="n">
-        <v>21.49</v>
+        <v>28.13</v>
       </c>
       <c r="F140" t="n">
-        <v>6.59</v>
+        <v>30.61</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[440.83, 258.69, 274.74]</t>
+          <t>[83.37, 145.64, 246.59]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[452.73, 308.4, 277.6]</t>
+          <t>[51.12, 132.39, 207.71]</t>
         </is>
       </c>
     </row>
@@ -5500,31 +5502,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>35.96</v>
+        <v>26.06</v>
       </c>
       <c r="E141" t="n">
-        <v>31.88</v>
+        <v>24.2</v>
       </c>
       <c r="F141" t="n">
-        <v>9.800000000000001</v>
+        <v>13.43</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[270.89, 268.32, 302.36]</t>
+          <t>[144.1, 243.02, 202.45]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[308.4, 277.6, 351.2]</t>
+          <t>[132.39, 207.71, 176.88]</t>
         </is>
       </c>
     </row>
@@ -5536,31 +5538,31 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>954.51</v>
+        <v>270.6</v>
       </c>
       <c r="E142" t="n">
-        <v>904.51</v>
+        <v>252.26</v>
       </c>
       <c r="F142" t="n">
-        <v>121.34</v>
+        <v>14.99</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[1830.91, 1813.96, 1798.25]</t>
+          <t>[1561.88, 1359.95, 1238.79]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[590.07, 843.96, 1295.56]</t>
+          <t>[1823.93, 1726.94, 1366.53]</t>
         </is>
       </c>
     </row>
@@ -5572,31 +5574,31 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>440.38</v>
+        <v>580.08</v>
       </c>
       <c r="E143" t="n">
-        <v>391.09</v>
+        <v>513.59</v>
       </c>
       <c r="F143" t="n">
-        <v>35.16</v>
+        <v>33.75</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[1449.24, 1415.06, 1379.42]</t>
+          <t>[2117.11, 2254.32, 2183.22]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[843.96, 1295.56, 1827.92]</t>
+          <t>[1726.94, 1366.53, 1920.41]</t>
         </is>
       </c>
     </row>
@@ -5608,31 +5610,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>445.83</v>
+        <v>1563.39</v>
       </c>
       <c r="E144" t="n">
-        <v>369.99</v>
+        <v>1055.05</v>
       </c>
       <c r="F144" t="n">
-        <v>21.2</v>
+        <v>26.75</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[1271.69, 1230.51, 1191.92]</t>
+          <t>[1752.15, 1819.25, 8404.45]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[1295.56, 1827.92, 1680.62]</t>
+          <t>[1366.53, 1920.41, 5726.09]</t>
         </is>
       </c>
     </row>
@@ -5644,31 +5646,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1653.95</v>
+        <v>900.65</v>
       </c>
       <c r="E145" t="n">
-        <v>1279.43</v>
+        <v>715.89</v>
       </c>
       <c r="F145" t="n">
-        <v>43.91</v>
+        <v>29.18</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[1234.56, 1196.1, 1157.62]</t>
+          <t>[1496.79, 7207.75, 369.84]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[1827.92, 1680.62, 3918.02]</t>
+          <t>[1920.41, 5726.09, 612.23]</t>
         </is>
       </c>
     </row>
@@ -5680,31 +5682,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1591.47</v>
+        <v>2231.06</v>
       </c>
       <c r="E146" t="n">
-        <v>1207.22</v>
+        <v>1352.02</v>
       </c>
       <c r="F146" t="n">
-        <v>41.05</v>
+        <v>32.22</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[1282.71, 1246.98, 1213.34]</t>
+          <t>[9587.42, 470.22, 821.23]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[1680.62, 3918.02, 1766.04]</t>
+          <t>[5726.09, 612.23, 873.95]</t>
         </is>
       </c>
     </row>
@@ -5716,31 +5718,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1573.74</v>
+        <v>276.12</v>
       </c>
       <c r="E147" t="n">
-        <v>1232.23</v>
+        <v>273.08</v>
       </c>
       <c r="F147" t="n">
-        <v>42.31</v>
+        <v>31.17</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[1302.38, 1270.51, 1238.41]</t>
+          <t>[361.55, 635.81, 975.26]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[3918.02, 1766.04, 1823.93]</t>
+          <t>[612.23, 873.95, 1305.68]</t>
         </is>
       </c>
     </row>
@@ -5752,31 +5754,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>142.39</v>
+        <v>159.13</v>
       </c>
       <c r="E148" t="n">
-        <v>127.28</v>
+        <v>147.82</v>
       </c>
       <c r="F148" t="n">
-        <v>7.19</v>
+        <v>13.62</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[1983.6, 1906.4, 1808.76]</t>
+          <t>[644.32, 1185.08, 1648.06]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[1766.04, 1823.93, 1726.94]</t>
+          <t>[873.95, 1305.68, 1741.28]</t>
         </is>
       </c>
     </row>
@@ -5788,31 +5790,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>270.6</v>
+        <v>116.43</v>
       </c>
       <c r="E149" t="n">
-        <v>252.26</v>
+        <v>101.17</v>
       </c>
       <c r="F149" t="n">
-        <v>14.99</v>
+        <v>5.69</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[1561.88, 1359.95, 1238.79]</t>
+          <t>[1331.05, 1906.32, 1893.17]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[1823.93, 1726.94, 1366.53]</t>
+          <t>[1305.68, 1741.28, 2006.25]</t>
         </is>
       </c>
     </row>
@@ -5824,31 +5826,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>580.08</v>
+        <v>147.3</v>
       </c>
       <c r="E150" t="n">
-        <v>513.59</v>
+        <v>143.78</v>
       </c>
       <c r="F150" t="n">
-        <v>33.75</v>
+        <v>5.94</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[2117.11, 2254.32, 2183.22]</t>
+          <t>[1900.92, 1907.08, 4495.5]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[1726.94, 1366.53, 1920.41]</t>
+          <t>[1741.28, 2006.25, 4668.04]</t>
         </is>
       </c>
     </row>
@@ -5860,31 +5862,31 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1563.39</v>
+        <v>587.88</v>
       </c>
       <c r="E151" t="n">
-        <v>1055.05</v>
+        <v>532.8099999999999</v>
       </c>
       <c r="F151" t="n">
-        <v>26.75</v>
+        <v>34.66</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[1752.15, 1819.25, 8404.45]</t>
+          <t>[1777.9, 4134.82, 1867.65]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[1366.53, 1920.41, 5726.09]</t>
+          <t>[2006.25, 4668.04, 1030.78]</t>
         </is>
       </c>
     </row>
@@ -5896,31 +5898,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1291.85</v>
+        <v>551.83</v>
       </c>
       <c r="E152" t="n">
-        <v>1252.29</v>
+        <v>462.18</v>
       </c>
       <c r="F152" t="n">
-        <v>144.85</v>
+        <v>17.99</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[2188.42, 2211.98, 2234.25]</t>
+          <t>[1425.5, 1876.15, 3161.06]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[721.24, 726.03, 3037.98]</t>
+          <t>[1529.73, 2717.96, 2720.57]</t>
         </is>
       </c>
     </row>
@@ -5932,31 +5934,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1090.52</v>
+        <v>393.15</v>
       </c>
       <c r="E153" t="n">
-        <v>1079.55</v>
+        <v>371.55</v>
       </c>
       <c r="F153" t="n">
-        <v>98.73</v>
+        <v>13.65</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[1760.35, 1750.89, 1740.83]</t>
+          <t>[2197.76, 3108.39, 2945.48]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[726.03, 3037.98, 823.6]</t>
+          <t>[2717.96, 2720.57, 2738.85]</t>
         </is>
       </c>
     </row>
@@ -5968,31 +5970,31 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1087.36</v>
+        <v>3572.22</v>
       </c>
       <c r="E154" t="n">
-        <v>1012.23</v>
+        <v>2711.88</v>
       </c>
       <c r="F154" t="n">
-        <v>91.31</v>
+        <v>56.09</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[1478.49, 1452.69, 1428.15]</t>
+          <t>[3989.12, 3613.62, 12672.59]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[3037.98, 823.6, 580.03]</t>
+          <t>[2720.57, 2738.85, 6680.27]</t>
         </is>
       </c>
     </row>
@@ -6004,31 +6006,31 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1448.9</v>
+        <v>958.98</v>
       </c>
       <c r="E155" t="n">
-        <v>1336.66</v>
+        <v>599.2</v>
       </c>
       <c r="F155" t="n">
-        <v>113.53</v>
+        <v>10.56</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[1655.7, 1641.68, 1627.32]</t>
+          <t>[2613.34, 8336.45, 673.66]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[823.6, 580.03, 3743.56]</t>
+          <t>[2738.85, 6680.27, 689.58]</t>
         </is>
       </c>
     </row>
@@ -6040,31 +6042,31 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1486.51</v>
+        <v>1777.08</v>
       </c>
       <c r="E156" t="n">
-        <v>1283.27</v>
+        <v>1069.04</v>
       </c>
       <c r="F156" t="n">
-        <v>100.29</v>
+        <v>22.21</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[1430.49, 1404.9, 1380.57]</t>
+          <t>[9755.91, 677.75, 753.96]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[580.03, 3743.56, 719.87]</t>
+          <t>[6680.27, 689.58, 634.31]</t>
         </is>
       </c>
     </row>
@@ -6076,31 +6078,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1500.55</v>
+        <v>335.7</v>
       </c>
       <c r="E157" t="n">
-        <v>1123.42</v>
+        <v>247.24</v>
       </c>
       <c r="F157" t="n">
-        <v>52.21</v>
+        <v>14.4</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[1214.19, 1183.37, 1152.34]</t>
+          <t>[586.33, 704.94, 2755.63]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[3743.56, 719.87, 1529.73]</t>
+          <t>[689.58, 634.31, 3323.46]</t>
         </is>
       </c>
     </row>
@@ -6112,31 +6114,31 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>102.29</v>
+        <v>187.63</v>
       </c>
       <c r="E158" t="n">
-        <v>80.28</v>
+        <v>143.19</v>
       </c>
       <c r="F158" t="n">
-        <v>6.13</v>
+        <v>9.18</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[765.86, 1698.88, 2692.27]</t>
+          <t>[732.37, 3014.44, 834.17]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[719.87, 1529.73, 2717.96]</t>
+          <t>[634.31, 3323.46, 811.68]</t>
         </is>
       </c>
     </row>
@@ -6148,31 +6150,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>551.83</v>
+        <v>282.71</v>
       </c>
       <c r="E159" t="n">
-        <v>462.18</v>
+        <v>205.85</v>
       </c>
       <c r="F159" t="n">
-        <v>17.99</v>
+        <v>11.74</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[1425.5, 1876.15, 3161.06]</t>
+          <t>[2847.16, 779.33, 534.89]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[1529.73, 2717.96, 2720.57]</t>
+          <t>[3323.46, 811.68, 643.8]</t>
         </is>
       </c>
     </row>
@@ -6184,31 +6186,31 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>393.15</v>
+        <v>155.66</v>
       </c>
       <c r="E160" t="n">
-        <v>371.55</v>
+        <v>117.68</v>
       </c>
       <c r="F160" t="n">
-        <v>13.65</v>
+        <v>6.55</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[2197.76, 3108.39, 2945.48]</t>
+          <t>[846.27, 586.51, 3760.67]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[2717.96, 2720.57, 2738.85]</t>
+          <t>[811.68, 643.8, 4021.84]</t>
         </is>
       </c>
     </row>
@@ -6220,31 +6222,31 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3572.22</v>
+        <v>186.11</v>
       </c>
       <c r="E161" t="n">
-        <v>2711.88</v>
+        <v>151.1</v>
       </c>
       <c r="F161" t="n">
-        <v>56.09</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[3989.12, 3613.62, 12672.59]</t>
+          <t>[579.93, 3717.57, 716.64]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[2720.57, 2738.85, 6680.27]</t>
+          <t>[643.8, 4021.84, 801.79]</t>
         </is>
       </c>
     </row>
@@ -6256,31 +6258,31 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>184.5</v>
+        <v>633.86</v>
       </c>
       <c r="E162" t="n">
-        <v>183.52</v>
+        <v>590.7</v>
       </c>
       <c r="F162" t="n">
-        <v>58.72</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[497.87, 498.94, 499.94]</t>
+          <t>[145.81, 202.1, 130.69]</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[340.5, 297.1, 308.6]</t>
+          <t>[521.6, 1111.5, 617.6]</t>
         </is>
       </c>
     </row>
@@ -6292,31 +6294,31 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>174.72</v>
+        <v>444.36</v>
       </c>
       <c r="E163" t="n">
-        <v>173.73</v>
+        <v>352.31</v>
       </c>
       <c r="F163" t="n">
-        <v>60.72</v>
+        <v>42.22</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[464.61, 463.32, 461.95]</t>
+          <t>[412.64, 297.38, 354.84]</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[297.1, 308.6, 263.0]</t>
+          <t>[1111.5, 617.6, 317.0]</t>
         </is>
       </c>
     </row>
@@ -6328,31 +6330,31 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>199.67</v>
+        <v>1141.69</v>
       </c>
       <c r="E164" t="n">
-        <v>185.91</v>
+        <v>764.26</v>
       </c>
       <c r="F164" t="n">
-        <v>45.86</v>
+        <v>165.93</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[423.59, 419.68, 415.94]</t>
+          <t>[274.34, 319.1, 2388.5]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[308.6, 263.0, 702.01]</t>
+          <t>[617.6, 317.0, 441.06]</t>
         </is>
       </c>
     </row>
@@ -6364,31 +6366,31 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>310.34</v>
+        <v>2706.93</v>
       </c>
       <c r="E165" t="n">
-        <v>287.07</v>
+        <v>1791.03</v>
       </c>
       <c r="F165" t="n">
-        <v>48.87</v>
+        <v>424.63</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[394.66, 389.59, 384.42]</t>
+          <t>[657.19, 5102.46, 710.11]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[263.0, 702.01, 801.55]</t>
+          <t>[317.0, 441.06, 338.6]</t>
         </is>
       </c>
     </row>
@@ -6400,31 +6402,31 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>327.7</v>
+        <v>1654.23</v>
       </c>
       <c r="E166" t="n">
-        <v>295.44</v>
+        <v>1076.24</v>
       </c>
       <c r="F166" t="n">
-        <v>48.6</v>
+        <v>255.66</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[364.06, 357.67, 351.6]</t>
+          <t>[3293.76, 506.45, 86.64]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[702.01, 801.55, 247.1]</t>
+          <t>[441.06, 338.6, 294.8]</t>
         </is>
       </c>
     </row>
@@ -6436,31 +6438,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>259.61</v>
+        <v>278.39</v>
       </c>
       <c r="E167" t="n">
-        <v>227.63</v>
+        <v>214.2</v>
       </c>
       <c r="F167" t="n">
-        <v>45</v>
+        <v>66.13</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[397.55, 393.25, 388.85]</t>
+          <t>[781.67, 104.81, 316.43]</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>[801.55, 247.1, 521.6]</t>
+          <t>[338.6, 294.8, 306.9]</t>
         </is>
       </c>
     </row>
@@ -6472,31 +6474,31 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>591.0599999999999</v>
+        <v>93.09</v>
       </c>
       <c r="E168" t="n">
-        <v>451.03</v>
+        <v>65.62</v>
       </c>
       <c r="F168" t="n">
-        <v>55.47</v>
+        <v>22.58</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[232.28, 128.5, 166.34]</t>
+          <t>[136.17, 295.0, 235.48]</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>[247.1, 521.6, 1111.5]</t>
+          <t>[294.8, 306.9, 261.8]</t>
         </is>
       </c>
     </row>
@@ -6508,31 +6510,31 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>633.86</v>
+        <v>11.72</v>
       </c>
       <c r="E169" t="n">
-        <v>590.7</v>
+        <v>10.68</v>
       </c>
       <c r="F169" t="n">
-        <v>77.56999999999999</v>
+        <v>2.54</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[145.81, 202.1, 130.69]</t>
+          <t>[315.86, 256.0, 681.73]</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>[521.6, 1111.5, 617.6]</t>
+          <t>[306.9, 261.8, 699.0]</t>
         </is>
       </c>
     </row>
@@ -6544,31 +6546,31 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>444.36</v>
+        <v>35.23</v>
       </c>
       <c r="E170" t="n">
-        <v>352.31</v>
+        <v>27.71</v>
       </c>
       <c r="F170" t="n">
-        <v>42.22</v>
+        <v>4.15</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[412.64, 297.38, 354.84]</t>
+          <t>[255.34, 679.92, 736.61]</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[1111.5, 617.6, 317.0]</t>
+          <t>[261.8, 699.0, 794.2]</t>
         </is>
       </c>
     </row>
@@ -6580,31 +6582,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1141.69</v>
+        <v>34.52</v>
       </c>
       <c r="E171" t="n">
-        <v>764.26</v>
+        <v>27.93</v>
       </c>
       <c r="F171" t="n">
-        <v>165.93</v>
+        <v>4.52</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[274.34, 319.1, 2388.5]</t>
+          <t>[681.16, 737.96, 237.19]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[617.6, 317.0, 441.06]</t>
+          <t>[699.0, 794.2, 246.9]</t>
         </is>
       </c>
     </row>
@@ -6616,31 +6618,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>64.12</v>
+        <v>87.37</v>
       </c>
       <c r="E172" t="n">
-        <v>50.61</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>13.34</v>
+        <v>8.42</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[457.63, 440.15, 539.19]</t>
+          <t>[682.79, 853.25, 707.98]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[351.38, 419.37, 514.38]</t>
+          <t>[799.28, 949.76, 711.61]</t>
         </is>
       </c>
     </row>
@@ -6652,31 +6654,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>88.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E173" t="n">
-        <v>55.85</v>
+        <v>71.5</v>
       </c>
       <c r="F173" t="n">
-        <v>6.79</v>
+        <v>7.75</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[431.08, 517.59, 747.15]</t>
+          <t>[863.03, 717.12, 794.64]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[419.37, 514.38, 899.78]</t>
+          <t>[949.76, 711.61, 916.89]</t>
         </is>
       </c>
     </row>
@@ -6688,31 +6690,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>93.31999999999999</v>
+        <v>183.45</v>
       </c>
       <c r="E174" t="n">
-        <v>62.48</v>
+        <v>140.42</v>
       </c>
       <c r="F174" t="n">
-        <v>7.12</v>
+        <v>11.13</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[514.69, 740.57, 802.71]</t>
+          <t>[719.45, 798.03, 1230.73]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[514.38, 899.78, 774.78]</t>
+          <t>[711.61, 916.89, 1525.3]</t>
         </is>
       </c>
     </row>
@@ -6724,31 +6726,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>143.73</v>
+        <v>179.36</v>
       </c>
       <c r="E175" t="n">
-        <v>124.71</v>
+        <v>139.82</v>
       </c>
       <c r="F175" t="n">
-        <v>12.53</v>
+        <v>11.8</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[741.86, 800.22, 947.91]</t>
+          <t>[799.41, 1238.09, 377.28]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[899.78, 774.78, 1138.67]</t>
+          <t>[916.89, 1525.3, 392.03]</t>
         </is>
       </c>
     </row>
@@ -6760,31 +6762,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>108.24</v>
+        <v>163.35</v>
       </c>
       <c r="E176" t="n">
-        <v>87.22</v>
+        <v>103.12</v>
       </c>
       <c r="F176" t="n">
-        <v>9.65</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[814.18, 960.84, 582.33]</t>
+          <t>[1243.02, 379.54, 438.21]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>[774.78, 1138.67, 537.89]</t>
+          <t>[1525.3, 392.03, 423.63]</t>
         </is>
       </c>
     </row>
@@ -6796,31 +6798,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>128.01</v>
+        <v>18.34</v>
       </c>
       <c r="E177" t="n">
-        <v>114.53</v>
+        <v>17.6</v>
       </c>
       <c r="F177" t="n">
-        <v>12.92</v>
+        <v>3.89</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[958.32, 578.84, 676.98]</t>
+          <t>[381.77, 444.8, 506.09]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[1138.67, 537.89, 799.28]</t>
+          <t>[392.03, 423.63, 527.44]</t>
         </is>
       </c>
     </row>
@@ -6832,31 +6834,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>87.15000000000001</v>
+        <v>76.22</v>
       </c>
       <c r="E178" t="n">
-        <v>83.34</v>
+        <v>57.37</v>
       </c>
       <c r="F178" t="n">
-        <v>10.85</v>
+        <v>7.86</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[587.77, 687.64, 861.26]</t>
+          <t>[447.14, 507.15, 775.93]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[537.89, 799.28, 949.76]</t>
+          <t>[423.63, 527.44, 904.24]</t>
         </is>
       </c>
     </row>
@@ -6868,31 +6870,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>87.37</v>
+        <v>81.25</v>
       </c>
       <c r="E179" t="n">
-        <v>72.20999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F179" t="n">
-        <v>8.42</v>
+        <v>8.02</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[682.79, 853.25, 707.98]</t>
+          <t>[505.1, 772.0, 776.39]</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[799.28, 949.76, 711.61]</t>
+          <t>[527.44, 904.24, 819.04]</t>
         </is>
       </c>
     </row>
@@ -6904,31 +6906,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>86.59999999999999</v>
+        <v>108.94</v>
       </c>
       <c r="E180" t="n">
-        <v>71.5</v>
+        <v>100.01</v>
       </c>
       <c r="F180" t="n">
-        <v>7.75</v>
+        <v>10.14</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[863.03, 717.12, 794.64]</t>
+          <t>[774.99, 780.09, 1026.41]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>[949.76, 711.61, 916.89]</t>
+          <t>[904.24, 819.04, 1158.24]</t>
         </is>
       </c>
     </row>
@@ -6940,31 +6942,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>183.45</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="E181" t="n">
-        <v>140.42</v>
+        <v>51.65</v>
       </c>
       <c r="F181" t="n">
-        <v>11.13</v>
+        <v>5.01</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[719.45, 798.03, 1230.73]</t>
+          <t>[789.81, 1039.45, 566.36]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[711.61, 916.89, 1525.3]</t>
+          <t>[819.04, 1158.24, 573.3]</t>
         </is>
       </c>
     </row>
@@ -6976,31 +6978,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11.36</v>
+        <v>52.59</v>
       </c>
       <c r="E182" t="n">
-        <v>9.800000000000001</v>
+        <v>51.34</v>
       </c>
       <c r="F182" t="n">
-        <v>9.83</v>
+        <v>10.53</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[301.59, 43.3, 184.31]</t>
+          <t>[1391.39, 657.67, 201.93]</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[299.48, 54.71, 200.2]</t>
+          <t>[1452.09, 692.96, 259.97]</t>
         </is>
       </c>
     </row>
@@ -7012,31 +7014,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>28.38</v>
+        <v>54.26</v>
       </c>
       <c r="E183" t="n">
-        <v>24.51</v>
+        <v>52.54</v>
       </c>
       <c r="F183" t="n">
-        <v>15.23</v>
+        <v>16.78</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[42.97, 182.89, 330.03]</t>
+          <t>[658.73, 203.03, 216.39]</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[54.71, 200.2, 285.56]</t>
+          <t>[692.96, 259.97, 282.85]</t>
         </is>
       </c>
     </row>
@@ -7048,31 +7050,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>43.42</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="E184" t="n">
-        <v>38.34</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="F184" t="n">
-        <v>12.28</v>
+        <v>22.76</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[190.35, 341.97, 449.5]</t>
+          <t>[204.18, 217.88, 337.89]</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[200.2, 285.56, 400.74]</t>
+          <t>[259.97, 282.85, 443.65]</t>
         </is>
       </c>
     </row>
@@ -7084,31 +7086,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>46.4</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="E185" t="n">
-        <v>43.98</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F185" t="n">
-        <v>12.62</v>
+        <v>18.5</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[343.29, 451.48, 447.13]</t>
+          <t>[220.69, 343.33, 292.85]</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[285.56, 400.74, 470.6]</t>
+          <t>[282.85, 443.65, 328.67]</t>
         </is>
       </c>
     </row>
@@ -7120,31 +7122,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>60.82</v>
+        <v>59.37</v>
       </c>
       <c r="E186" t="n">
-        <v>55.45</v>
+        <v>50.5</v>
       </c>
       <c r="F186" t="n">
-        <v>9.119999999999999</v>
+        <v>22.34</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[444.79, 438.44, 1036.72]</t>
+          <t>[349.03, 298.64, 46.6]</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[400.74, 470.6, 946.59]</t>
+          <t>[443.65, 328.67, 73.46]</t>
         </is>
       </c>
     </row>
@@ -7156,31 +7158,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>60.17</v>
+        <v>30.41</v>
       </c>
       <c r="E187" t="n">
-        <v>57.79</v>
+        <v>29.89</v>
       </c>
       <c r="F187" t="n">
-        <v>6.66</v>
+        <v>19.98</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[434.33, 1023.68, 1392.07]</t>
+          <t>[302.77, 47.46, 188.72]</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[470.6, 946.59, 1452.09]</t>
+          <t>[328.67, 73.46, 226.5]</t>
         </is>
       </c>
     </row>
@@ -7192,31 +7194,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>59.28</v>
+        <v>25.85</v>
       </c>
       <c r="E188" t="n">
-        <v>54.74</v>
+        <v>21.66</v>
       </c>
       <c r="F188" t="n">
-        <v>5.58</v>
+        <v>17.34</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[1031.67, 1403.28, 662.63]</t>
+          <t>[47.69, 190.0, 326.92]</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[946.59, 1452.09, 692.96]</t>
+          <t>[73.46, 226.5, 324.2]</t>
         </is>
       </c>
     </row>
@@ -7228,31 +7230,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>52.59</v>
+        <v>28.33</v>
       </c>
       <c r="E189" t="n">
-        <v>51.34</v>
+        <v>27.83</v>
       </c>
       <c r="F189" t="n">
-        <v>10.53</v>
+        <v>8.85</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[1391.39, 657.67, 201.93]</t>
+          <t>[200.33, 346.52, 466.64]</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[1452.09, 692.96, 259.97]</t>
+          <t>[226.5, 324.2, 431.65]</t>
         </is>
       </c>
     </row>
@@ -7264,31 +7266,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>54.26</v>
+        <v>32.03</v>
       </c>
       <c r="E190" t="n">
-        <v>52.54</v>
+        <v>28.1</v>
       </c>
       <c r="F190" t="n">
-        <v>16.78</v>
+        <v>7.2</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[658.73, 203.03, 216.39]</t>
+          <t>[354.19, 477.56, 500.68]</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>[692.96, 259.97, 282.85]</t>
+          <t>[324.2, 431.65, 492.27]</t>
         </is>
       </c>
     </row>
@@ -7300,31 +7302,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>78.56999999999999</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="E191" t="n">
-        <v>75.51000000000001</v>
+        <v>57.52</v>
       </c>
       <c r="F191" t="n">
-        <v>22.76</v>
+        <v>7.97</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>[204.18, 217.88, 337.89]</t>
+          <t>[475.98, 498.96, 1111.16]</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>[259.97, 282.85, 443.65]</t>
+          <t>[431.65, 492.27, 989.64]</t>
         </is>
       </c>
     </row>
@@ -7336,31 +7338,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>971.3099999999999</v>
+        <v>233.24</v>
       </c>
       <c r="E192" t="n">
-        <v>933.7</v>
+        <v>216.01</v>
       </c>
       <c r="F192" t="n">
-        <v>19.2</v>
+        <v>5.53</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[6172.78, 5608.28, 5617.96]</t>
+          <t>[3689.74, 4387.01, 4542.82]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[4865.05, 4811.11, 4921.76]</t>
+          <t>[3378.76, 4625.15, 4443.92]</t>
         </is>
       </c>
     </row>
@@ -7372,31 +7374,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>550.6</v>
+        <v>838.53</v>
       </c>
       <c r="E193" t="n">
-        <v>533.71</v>
+        <v>586.97</v>
       </c>
       <c r="F193" t="n">
-        <v>11.94</v>
+        <v>11.23</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[5385.16, 5273.31, 4708.83]</t>
+          <t>[4286.23, 4434.18, 3989.81]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[4811.11, 4921.76, 4033.29]</t>
+          <t>[4625.15, 4443.92, 5402.06]</t>
         </is>
       </c>
     </row>
@@ -7408,31 +7410,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>335.29</v>
+        <v>2101.75</v>
       </c>
       <c r="E194" t="n">
-        <v>305.43</v>
+        <v>1592.77</v>
       </c>
       <c r="F194" t="n">
-        <v>7.47</v>
+        <v>21.4</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[5072.54, 4519.78, 4115.03]</t>
+          <t>[4481.72, 4035.4, 5492.51]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[4921.76, 4033.29, 3836.02]</t>
+          <t>[4443.92, 5402.06, 8866.36]</t>
         </is>
       </c>
     </row>
@@ -7444,31 +7446,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>482.46</v>
+        <v>2146.61</v>
       </c>
       <c r="E195" t="n">
-        <v>444.4</v>
+        <v>1720.61</v>
       </c>
       <c r="F195" t="n">
-        <v>10.04</v>
+        <v>24.03</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[4466.18, 4056.34, 4308.33]</t>
+          <t>[3992.67, 5441.43, 4120.45]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[4033.29, 3836.02, 4988.31]</t>
+          <t>[5402.06, 8866.36, 4447.97]</t>
         </is>
       </c>
     </row>
@@ -7480,31 +7482,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1034.09</v>
+        <v>1867.28</v>
       </c>
       <c r="E196" t="n">
-        <v>844.21</v>
+        <v>1256.02</v>
       </c>
       <c r="F196" t="n">
-        <v>29.38</v>
+        <v>16.42</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[3999.61, 4236.82, 3968.44]</t>
+          <t>[5664.77, 4322.07, 3826.32]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[3836.02, 4988.31, 2350.88]</t>
+          <t>[8866.36, 4447.97, 4266.88]</t>
         </is>
       </c>
     </row>
@@ -7516,31 +7518,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1052.38</v>
+        <v>278.21</v>
       </c>
       <c r="E197" t="n">
-        <v>956.62</v>
+        <v>237.07</v>
       </c>
       <c r="F197" t="n">
-        <v>32.38</v>
+        <v>5.32</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[4166.84, 3899.37, 3878.68]</t>
+          <t>[4546.5, 4092.47, 4101.95]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[4988.31, 2350.88, 3378.76]</t>
+          <t>[4447.97, 4266.88, 4540.22]</t>
         </is>
       </c>
     </row>
@@ -7552,31 +7554,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1042.31</v>
+        <v>343.43</v>
       </c>
       <c r="E198" t="n">
-        <v>833.85</v>
+        <v>325.28</v>
       </c>
       <c r="F198" t="n">
-        <v>31.43</v>
+        <v>7.64</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[4029.31, 4017.6, 4809.44]</t>
+          <t>[4086.58, 4092.99, 3591.43]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[2350.88, 3378.76, 4625.15]</t>
+          <t>[4266.88, 4540.22, 3939.72]</t>
         </is>
       </c>
     </row>
@@ -7588,31 +7590,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>233.24</v>
+        <v>373.72</v>
       </c>
       <c r="E199" t="n">
-        <v>216.01</v>
+        <v>365.85</v>
       </c>
       <c r="F199" t="n">
-        <v>5.53</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[3689.74, 4387.01, 4542.82]</t>
+          <t>[4079.5, 3576.83, 3357.95]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[3378.76, 4625.15, 4443.92]</t>
+          <t>[4540.22, 3939.72, 3631.9]</t>
         </is>
       </c>
     </row>
@@ -7624,31 +7626,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>838.53</v>
+        <v>208.47</v>
       </c>
       <c r="E200" t="n">
-        <v>586.97</v>
+        <v>194.48</v>
       </c>
       <c r="F200" t="n">
-        <v>11.23</v>
+        <v>5.08</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[4286.23, 4434.18, 3989.81]</t>
+          <t>[3654.98, 3434.14, 3814.06]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[4625.15, 4443.92, 5402.06]</t>
+          <t>[3939.72, 3631.9, 3915.0]</t>
         </is>
       </c>
     </row>
@@ -7660,31 +7662,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2101.75</v>
+        <v>232.16</v>
       </c>
       <c r="E201" t="n">
-        <v>1592.77</v>
+        <v>200.6</v>
       </c>
       <c r="F201" t="n">
-        <v>21.4</v>
+        <v>6.81</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[4481.72, 4035.4, 5492.51]</t>
+          <t>[3457.91, 3842.34, 2931.63]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[4443.92, 5402.06, 8866.36]</t>
+          <t>[3631.9, 3915.0, 2576.47]</t>
         </is>
       </c>
     </row>
